--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119916167</v>
+        <v>119916189</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585364</v>
+        <v>585362</v>
       </c>
       <c r="R4" t="n">
-        <v>6429672</v>
+        <v>6429688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916189</v>
+        <v>119916167</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,30 +1021,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585364</v>
       </c>
       <c r="R5" t="n">
-        <v>6429688</v>
+        <v>6429672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916298</v>
+        <v>119916167</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -708,7 +708,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585369</v>
+        <v>585364</v>
       </c>
       <c r="R2" t="n">
-        <v>6429686</v>
+        <v>6429672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1009,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916167</v>
+        <v>119916298</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1042,11 +1046,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585364</v>
+        <v>585369</v>
       </c>
       <c r="R5" t="n">
-        <v>6429672</v>
+        <v>6429686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916167</v>
+        <v>119916298</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,11 +708,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585364</v>
+        <v>585369</v>
       </c>
       <c r="R2" t="n">
-        <v>6429672</v>
+        <v>6429686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119916246</v>
+        <v>119916167</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +818,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -840,7 +840,7 @@
         <v>585364</v>
       </c>
       <c r="R3" t="n">
-        <v>6429676</v>
+        <v>6429672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>119916189</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916298</v>
+        <v>119916246</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585369</v>
+        <v>585364</v>
       </c>
       <c r="R5" t="n">
-        <v>6429686</v>
+        <v>6429676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916298</v>
+        <v>119916189</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585369</v>
+        <v>585362</v>
       </c>
       <c r="R2" t="n">
-        <v>6429686</v>
+        <v>6429688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119916167</v>
+        <v>119916246</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -818,11 +822,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -840,7 +840,7 @@
         <v>585364</v>
       </c>
       <c r="R3" t="n">
-        <v>6429672</v>
+        <v>6429676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119916189</v>
+        <v>119916298</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,32 +911,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585362</v>
+        <v>585369</v>
       </c>
       <c r="R4" t="n">
-        <v>6429688</v>
+        <v>6429686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916246</v>
+        <v>119916167</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1046,7 +1042,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1064,7 +1064,7 @@
         <v>585364</v>
       </c>
       <c r="R5" t="n">
-        <v>6429676</v>
+        <v>6429672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916189</v>
+        <v>119916246</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585362</v>
+        <v>585364</v>
       </c>
       <c r="R2" t="n">
-        <v>6429688</v>
+        <v>6429676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119916246</v>
+        <v>119916167</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -822,7 +818,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -840,7 +840,7 @@
         <v>585364</v>
       </c>
       <c r="R3" t="n">
-        <v>6429676</v>
+        <v>6429672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119916298</v>
+        <v>119916189</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,28 +911,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585369</v>
+        <v>585362</v>
       </c>
       <c r="R4" t="n">
-        <v>6429686</v>
+        <v>6429688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916167</v>
+        <v>119916298</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1042,11 +1046,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585364</v>
+        <v>585369</v>
       </c>
       <c r="R5" t="n">
-        <v>6429672</v>
+        <v>6429686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916246</v>
+        <v>119916298</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585364</v>
+        <v>585369</v>
       </c>
       <c r="R2" t="n">
-        <v>6429676</v>
+        <v>6429686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119916167</v>
+        <v>119916246</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -818,11 +818,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -840,7 +836,7 @@
         <v>585364</v>
       </c>
       <c r="R3" t="n">
-        <v>6429672</v>
+        <v>6429676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119916189</v>
+        <v>119916167</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585362</v>
+        <v>585364</v>
       </c>
       <c r="R4" t="n">
-        <v>6429688</v>
+        <v>6429672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916298</v>
+        <v>119916189</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,28 +1021,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585369</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>6429686</v>
+        <v>6429688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119916298</v>
+        <v>119916189</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585369</v>
+        <v>585362</v>
       </c>
       <c r="R2" t="n">
-        <v>6429686</v>
+        <v>6429688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1009,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119916189</v>
+        <v>119916298</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,32 +1025,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585369</v>
       </c>
       <c r="R5" t="n">
-        <v>6429688</v>
+        <v>6429686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35236-2024 artfynd.xlsx
+++ b/artfynd/A 35236-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119916189</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119916246</v>
+        <v>119916167</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,7 +812,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -840,7 +834,7 @@
         <v>585364</v>
       </c>
       <c r="R3" t="n">
-        <v>6429676</v>
+        <v>6429672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119916167</v>
+        <v>119916246</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,11 +921,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -954,7 +939,7 @@
         <v>585364</v>
       </c>
       <c r="R4" t="n">
-        <v>6429672</v>
+        <v>6429676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,12 +1001,7 @@
         <v>119916298</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
